--- a/results/[6_green_friendly]_#_fix_cost.xlsx
+++ b/results/[6_green_friendly]_#_fix_cost.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="2025" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2030" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="2035" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="2040" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="2045" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="2050" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2030" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2035" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2040" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2045" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2050" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -512,13 +512,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3125.119287316165</v>
+        <v>8944.859755583977</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>4927.788459670779</v>
       </c>
       <c r="C2" t="n">
-        <v>38683.01019569611</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -527,13 +527,13 @@
         <v>231779.209144148</v>
       </c>
       <c r="F2" t="n">
-        <v>7546.507577201783</v>
+        <v>15147.7828936298</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>2027.422343033684</v>
+        <v>2060.836995567114</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -551,10 +551,10 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1894.610970861271</v>
+        <v>2402.2151999159</v>
       </c>
       <c r="O2" t="n">
-        <v>1596.959756313929</v>
+        <v>1573.80512018487</v>
       </c>
     </row>
   </sheetData>
@@ -650,13 +650,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5592.841625345535</v>
+        <v>65344.25270523081</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>4927.788459670779</v>
       </c>
       <c r="C2" t="n">
-        <v>158331.0001646095</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -665,13 +665,13 @@
         <v>231779.209144148</v>
       </c>
       <c r="F2" t="n">
-        <v>13162.01156291295</v>
+        <v>15147.7828936298</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>6555.616545050024</v>
+        <v>6557.287277676696</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -689,10 +689,10 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>6037.449078019277</v>
+        <v>10386.23736416328</v>
       </c>
       <c r="O2" t="n">
-        <v>5007.288439540145</v>
+        <v>5004.787191696439</v>
       </c>
     </row>
   </sheetData>
@@ -788,13 +788,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>24989.03564310195</v>
+        <v>104303.8307331068</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>4927.788459670779</v>
       </c>
       <c r="C2" t="n">
-        <v>233797.8217711074</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -803,13 +803,13 @@
         <v>231779.209144148</v>
       </c>
       <c r="F2" t="n">
-        <v>13276.08564128262</v>
+        <v>15147.7828936298</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>9705.535366320997</v>
+        <v>9704.310548747968</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -824,13 +824,13 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2122.058053890605</v>
       </c>
       <c r="N2" t="n">
-        <v>10316.13445312728</v>
+        <v>19095.43207858181</v>
       </c>
       <c r="O2" t="n">
-        <v>7412.70627513708</v>
+        <v>7409.258379664972</v>
       </c>
     </row>
   </sheetData>
@@ -926,13 +926,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>24989.03564310195</v>
+        <v>104303.8307331068</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>4927.788459670779</v>
       </c>
       <c r="C2" t="n">
-        <v>233797.8217711074</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -941,13 +941,13 @@
         <v>231779.209144148</v>
       </c>
       <c r="F2" t="n">
-        <v>13276.08564128262</v>
+        <v>15147.7828936298</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>9705.535366320997</v>
+        <v>9704.310548747968</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -962,13 +962,13 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2122.058053890605</v>
       </c>
       <c r="N2" t="n">
-        <v>11242.41425508182</v>
+        <v>20145.89593014852</v>
       </c>
       <c r="O2" t="n">
-        <v>7412.70627513708</v>
+        <v>7409.258379664972</v>
       </c>
     </row>
   </sheetData>
@@ -1064,13 +1064,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>31125.48275843248</v>
+        <v>104303.8307331068</v>
       </c>
       <c r="B2" t="n">
-        <v>154.4757918726473</v>
+        <v>4927.788459670779</v>
       </c>
       <c r="C2" t="n">
-        <v>233797.8217711074</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -1079,13 +1079,13 @@
         <v>231779.209144148</v>
       </c>
       <c r="F2" t="n">
-        <v>13276.08564128262</v>
+        <v>15147.7828936298</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>9705.535366320997</v>
+        <v>9704.310548747968</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -1100,13 +1100,13 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2122.058053890605</v>
       </c>
       <c r="N2" t="n">
-        <v>13513.47261752928</v>
+        <v>20145.89593014852</v>
       </c>
       <c r="O2" t="n">
-        <v>8079.009742155169</v>
+        <v>8075.067026403487</v>
       </c>
     </row>
   </sheetData>
@@ -1202,13 +1202,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>31125.48275843248</v>
+        <v>104303.8307331068</v>
       </c>
       <c r="B2" t="n">
-        <v>154.4757918726473</v>
+        <v>18131.3361506606</v>
       </c>
       <c r="C2" t="n">
-        <v>233797.8217711074</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -1217,13 +1217,13 @@
         <v>231779.209144148</v>
       </c>
       <c r="F2" t="n">
-        <v>13276.08564128262</v>
+        <v>15147.7828936298</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>9705.535366320997</v>
+        <v>9704.310548747968</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -1238,13 +1238,13 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2122.058053890605</v>
       </c>
       <c r="N2" t="n">
-        <v>13513.47261752928</v>
+        <v>20145.89593014852</v>
       </c>
       <c r="O2" t="n">
-        <v>8079.009742155169</v>
+        <v>8075.067026403487</v>
       </c>
     </row>
   </sheetData>

--- a/results/[6_green_friendly]_#_fix_cost.xlsx
+++ b/results/[6_green_friendly]_#_fix_cost.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="2025" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2030" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="2035" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="2040" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="2045" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="2050" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2030" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2035" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2040" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2045" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2050" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -512,13 +512,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2632.53230893218</v>
+        <v>8944.859755583977</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>4927.788459670779</v>
       </c>
       <c r="C2" t="n">
-        <v>41705.16887168352</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -527,13 +527,13 @@
         <v>231779.209144148</v>
       </c>
       <c r="F2" t="n">
-        <v>6879.276884578626</v>
+        <v>15147.7828936298</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>2138.767371038613</v>
+        <v>2060.836995567114</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -551,10 +551,10 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>2058.510482113492</v>
+        <v>2402.2151999159</v>
       </c>
       <c r="O2" t="n">
-        <v>1508.259426691686</v>
+        <v>1573.80512018487</v>
       </c>
     </row>
   </sheetData>
@@ -650,13 +650,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3996.663335846843</v>
+        <v>65344.25270523081</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>4927.788459670779</v>
       </c>
       <c r="C2" t="n">
-        <v>160869.2240877219</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -665,13 +665,13 @@
         <v>231779.209144148</v>
       </c>
       <c r="F2" t="n">
-        <v>13141.99464213426</v>
+        <v>15147.7828936298</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>6389.589810160347</v>
+        <v>6557.287277676696</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -689,10 +689,10 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>7532.666192049068</v>
+        <v>10386.23736416328</v>
       </c>
       <c r="O2" t="n">
-        <v>4227.32692574227</v>
+        <v>5004.787191696439</v>
       </c>
     </row>
   </sheetData>
@@ -788,13 +788,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>15235.5554636059</v>
+        <v>104303.8307331068</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>4927.788459670779</v>
       </c>
       <c r="C2" t="n">
-        <v>250229.6710899786</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -803,13 +803,13 @@
         <v>231779.209144148</v>
       </c>
       <c r="F2" t="n">
-        <v>14689.97692757889</v>
+        <v>15147.7828936298</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>9355.016094070601</v>
+        <v>9704.310548747968</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -824,13 +824,13 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2122.058053890605</v>
       </c>
       <c r="N2" t="n">
-        <v>12050.09905600459</v>
+        <v>19095.43207858181</v>
       </c>
       <c r="O2" t="n">
-        <v>7656.910856883376</v>
+        <v>7409.258379664972</v>
       </c>
     </row>
   </sheetData>
@@ -926,13 +926,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>15235.5554636059</v>
+        <v>104303.8307331068</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>4927.788459670779</v>
       </c>
       <c r="C2" t="n">
-        <v>250229.6710899786</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -941,13 +941,13 @@
         <v>231779.209144148</v>
       </c>
       <c r="F2" t="n">
-        <v>14689.97692757889</v>
+        <v>15147.7828936298</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>9355.016094070601</v>
+        <v>9704.310548747968</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -962,13 +962,13 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2122.058053890605</v>
       </c>
       <c r="N2" t="n">
-        <v>12050.09905600459</v>
+        <v>20145.89593014852</v>
       </c>
       <c r="O2" t="n">
-        <v>7656.910856883376</v>
+        <v>7409.258379664972</v>
       </c>
     </row>
   </sheetData>
@@ -1064,13 +1064,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>15235.5554636059</v>
+        <v>104303.8307331068</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>4927.788459670779</v>
       </c>
       <c r="C2" t="n">
-        <v>250229.6710899786</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -1079,13 +1079,13 @@
         <v>231779.209144148</v>
       </c>
       <c r="F2" t="n">
-        <v>14689.97692757889</v>
+        <v>15147.7828936298</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>9355.016094070601</v>
+        <v>9704.310548747968</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -1100,13 +1100,13 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2122.058053890605</v>
       </c>
       <c r="N2" t="n">
-        <v>12050.09905600459</v>
+        <v>20145.89593014852</v>
       </c>
       <c r="O2" t="n">
-        <v>7656.910856883376</v>
+        <v>8075.067026403487</v>
       </c>
     </row>
   </sheetData>
@@ -1202,13 +1202,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>15235.5554636059</v>
+        <v>104303.8307331068</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>18131.3361506606</v>
       </c>
       <c r="C2" t="n">
-        <v>250229.6710899786</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -1217,13 +1217,13 @@
         <v>231779.209144148</v>
       </c>
       <c r="F2" t="n">
-        <v>14689.97692757889</v>
+        <v>15147.7828936298</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>9355.016094070601</v>
+        <v>9704.310548747968</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -1238,13 +1238,13 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2122.058053890605</v>
       </c>
       <c r="N2" t="n">
-        <v>12050.09905600459</v>
+        <v>20145.89593014852</v>
       </c>
       <c r="O2" t="n">
-        <v>7656.910856883376</v>
+        <v>8075.067026403487</v>
       </c>
     </row>
   </sheetData>
